--- a/data/trans_orig/P77_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P77_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según cual es la persona sustentadora principal del hogar en 2023</t>
+          <t>Población según cual es la persona sustentadora principal del hogar en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>299512</t>
+          <t>303461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>349571</t>
+          <t>349992</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>232062</t>
+          <t>233286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>267603</t>
+          <t>270486</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>548845</t>
+          <t>549701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>611320</t>
+          <t>609217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17426</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>14917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25218</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44197</t>
+          <t>44811</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92128</t>
+          <t>91750</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39722</t>
+          <t>37251</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73424</t>
+          <t>71508</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>90973</t>
+          <t>91727</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>151087</t>
+          <t>152217</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63987</t>
+          <t>64556</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108668</t>
+          <t>105820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102135</t>
+          <t>112032</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210016</t>
+          <t>208820</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>196335</t>
+          <t>195493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>296120</t>
+          <t>296991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>313643</t>
+          <t>317109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>358068</t>
+          <t>357840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>300355</t>
+          <t>300099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>408900</t>
+          <t>399181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>637411</t>
+          <t>635692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>737165</t>
+          <t>737840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30782</t>
+          <t>30218</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56881</t>
+          <t>58033</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132042</t>
+          <t>130698</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>198061</t>
+          <t>197999</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>181164</t>
+          <t>184399</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>241016</t>
+          <t>242067</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187540</t>
+          <t>185940</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239867</t>
+          <t>210729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>478773</t>
+          <t>477565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>504755</t>
+          <t>505561</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>271544</t>
+          <t>269312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>405558</t>
+          <t>404676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>717829</t>
+          <t>733861</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>906229</t>
+          <t>905994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73777</t>
+          <t>73711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193490</t>
+          <t>192085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>252649</t>
+          <t>252380</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>163922</t>
+          <t>173091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>339450</t>
+          <t>342017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7867</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>812898</t>
+          <t>812970</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>868359</t>
+          <t>868432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>455831</t>
+          <t>455767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>515660</t>
+          <t>516539</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1255534</t>
+          <t>1252272</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1435138</t>
+          <t>1425646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29154</t>
+          <t>29493</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214931</t>
+          <t>212886</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248661</t>
+          <t>249422</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>229959</t>
+          <t>230189</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273343</t>
+          <t>272560</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -2667,97 +2667,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1623</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>1049</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1279</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>532080</t>
+          <t>531741</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>548346</t>
+          <t>548130</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>299244</t>
+          <t>298483</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>332974</t>
+          <t>335019</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>835796</t>
+          <t>836579</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>879180</t>
+          <t>878950</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19894</t>
+          <t>19898</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>269273</t>
+          <t>269250</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>513659</t>
+          <t>505350</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>241240</t>
+          <t>242522</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>656907</t>
+          <t>670750</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -3123,97 +3123,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1238</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>1341</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>348271</t>
+          <t>348267</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>359573</t>
+          <t>359748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>94709</t>
+          <t>103018</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>339095</t>
+          <t>339118</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>319626</t>
+          <t>305783</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>735293</t>
+          <t>734011</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,16%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>225182</t>
+          <t>225050</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>253206</t>
+          <t>255144</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>224745</t>
+          <t>225339</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>261448</t>
+          <t>261694</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -3579,97 +3579,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>927</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>275382</t>
+          <t>275605</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>281249</t>
+          <t>281207</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>172625</t>
+          <t>170687</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>200649</t>
+          <t>200781</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>447142</t>
+          <t>446896</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>483845</t>
+          <t>483251</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>432517</t>
+          <t>415608</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>614949</t>
+          <t>615693</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1539669</t>
+          <t>1536398</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2086105</t>
+          <t>2073449</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1994149</t>
+          <t>1996506</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2727441</t>
+          <t>2648552</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>13801</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>261254</t>
+          <t>269368</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>22895</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>277996</t>
+          <t>272694</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2833918</t>
+          <t>2835359</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3021578</t>
+          <t>3035655</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1558856</t>
+          <t>1582595</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2104820</t>
+          <t>2110337</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4397831</t>
+          <t>4481377</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5094285</t>
+          <t>5103954</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
